--- a/input/timetable/Биология_.xlsx
+++ b/input/timetable/Биология_.xlsx
@@ -1134,7 +1134,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1286,37 +1286,82 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1341,12 +1386,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1379,6 +1418,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1400,76 +1442,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1479,15 +1530,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1510,67 +1552,31 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1624,32 +1630,59 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1657,12 +1690,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1677,31 +1705,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2122,11 +2125,11 @@
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -2149,46 +2152,46 @@
       <c r="B10" s="19">
         <v>1</v>
       </c>
-      <c r="C10" s="126"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="128"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="80"/>
     </row>
     <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20"/>
       <c r="B11" s="21">
         <v>2</v>
       </c>
-      <c r="C11" s="116" t="s">
+      <c r="C11" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="85"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="66"/>
     </row>
     <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20"/>
       <c r="B12" s="21">
         <v>3</v>
       </c>
-      <c r="C12" s="133" t="s">
+      <c r="C12" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="135"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="88"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="22"/>
       <c r="B13" s="23">
         <v>5</v>
       </c>
-      <c r="C13" s="123" t="s">
+      <c r="C13" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="125"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
@@ -2197,50 +2200,50 @@
       <c r="B14" s="25">
         <v>1</v>
       </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20"/>
       <c r="B15" s="21">
         <v>2</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="85"/>
+      <c r="F15" s="66"/>
     </row>
     <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20"/>
       <c r="B16" s="21">
         <v>3</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67" t="s">
+      <c r="D16" s="73"/>
+      <c r="E16" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="68"/>
+      <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="27"/>
       <c r="B17" s="23">
         <v>4</v>
       </c>
-      <c r="C17" s="129" t="s">
+      <c r="C17" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="130"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="85"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
@@ -2249,42 +2252,42 @@
       <c r="B18" s="25">
         <v>1</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="69"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20"/>
       <c r="B19" s="21">
         <v>2</v>
       </c>
-      <c r="C19" s="116" t="s">
+      <c r="C19" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="85"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66"/>
     </row>
     <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20"/>
       <c r="B20" s="21">
         <v>3</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24" t="s">
@@ -2293,48 +2296,48 @@
       <c r="B22" s="25">
         <v>1</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64" t="s">
+      <c r="C22" s="127"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="65"/>
+      <c r="F22" s="129"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20"/>
       <c r="B23" s="21">
         <v>2</v>
       </c>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="84" t="s">
+      <c r="C23" s="95"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="85"/>
+      <c r="F23" s="66"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20"/>
       <c r="B24" s="21">
         <v>3</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="121" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="111"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="123"/>
     </row>
     <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="27"/>
       <c r="B25" s="23">
         <v>4</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="75"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="117"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="24" t="s">
@@ -2343,44 +2346,44 @@
       <c r="B26" s="25">
         <v>1</v>
       </c>
-      <c r="C26" s="112" t="s">
+      <c r="C26" s="124" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="114"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="126"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28"/>
       <c r="B27" s="21">
         <v>2</v>
       </c>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="81"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="94"/>
     </row>
     <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="28"/>
       <c r="B28" s="21"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="91"/>
     </row>
     <row r="29" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="29"/>
       <c r="B29" s="23">
         <v>5</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
     </row>
     <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="30" t="s">
@@ -2389,98 +2392,98 @@
       <c r="B30" s="25">
         <v>1</v>
       </c>
-      <c r="C30" s="92" t="s">
+      <c r="C30" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="94"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="105"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="31"/>
       <c r="B31" s="21">
         <v>2</v>
       </c>
-      <c r="C31" s="89"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="91"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="102"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="32"/>
       <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C32" s="101"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="103"/>
+      <c r="C32" s="112"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="114"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="33"/>
       <c r="B33" s="23">
         <v>4</v>
       </c>
-      <c r="C33" s="104"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="75"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
     </row>
     <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="34"/>
       <c r="B34" s="35"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="100"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="36"/>
       <c r="B35" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="106" t="s">
+      <c r="C35" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="108"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="38"/>
       <c r="B36" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="95" t="s">
+      <c r="C36" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="97"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="108"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="38"/>
       <c r="B37" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="95" t="s">
+      <c r="C37" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="97"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="108"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="29"/>
       <c r="B38" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="86" t="s">
+      <c r="C38" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="88"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="99"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
@@ -2500,20 +2503,12 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C23:D23"/>
@@ -2530,12 +2525,20 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2566,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2663,11 +2666,11 @@
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -2690,50 +2693,50 @@
       <c r="B10" s="19">
         <v>1</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="103" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
     </row>
     <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20"/>
       <c r="B11" s="21">
         <v>2</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67" t="s">
+      <c r="D11" s="73"/>
+      <c r="E11" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="68"/>
+      <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="109" t="s">
+      <c r="C12" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="111"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="123"/>
     </row>
     <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
       <c r="B13" s="23">
         <v>6</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="144"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="147"/>
     </row>
     <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
@@ -2742,50 +2745,50 @@
       <c r="B14" s="25">
         <v>3</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20"/>
       <c r="B15" s="21">
         <v>4</v>
       </c>
-      <c r="C15" s="166" t="s">
+      <c r="C15" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167" t="s">
+      <c r="D15" s="149"/>
+      <c r="E15" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="170"/>
+      <c r="F15" s="152"/>
     </row>
     <row r="16" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20"/>
       <c r="B16" s="21">
         <v>5</v>
       </c>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169" t="s">
+      <c r="D16" s="151"/>
+      <c r="E16" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="171"/>
+      <c r="F16" s="153"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="27"/>
       <c r="B17" s="23">
         <v>6</v>
       </c>
-      <c r="C17" s="160"/>
-      <c r="D17" s="161"/>
-      <c r="E17" s="161"/>
-      <c r="F17" s="162"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
@@ -2794,42 +2797,42 @@
       <c r="B18" s="25">
         <v>1</v>
       </c>
-      <c r="C18" s="163"/>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="165"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="144"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20"/>
       <c r="B19" s="21">
         <v>2</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="C19" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="111"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="123"/>
     </row>
     <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20"/>
       <c r="B20" s="21">
         <v>3</v>
       </c>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="174"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="156"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
       <c r="B21" s="23">
         <v>4</v>
       </c>
-      <c r="C21" s="157"/>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="159"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="138"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24" t="s">
@@ -2838,165 +2841,194 @@
       <c r="B22" s="25">
         <v>1</v>
       </c>
-      <c r="C22" s="136" t="s">
+      <c r="C22" s="157" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="138"/>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
+      <c r="F22" s="159"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20"/>
       <c r="B23" s="21">
         <v>2</v>
       </c>
-      <c r="C23" s="139"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="141"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="162"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="27"/>
       <c r="B24" s="23">
         <v>3</v>
       </c>
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="143"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="144"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D24" s="146"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="147"/>
+    </row>
+    <row r="25" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="28"/>
+      <c r="B26" s="19">
         <v>3</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C26" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="94"/>
-    </row>
-    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28"/>
-      <c r="B26" s="21">
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
+    </row>
+    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="28"/>
+      <c r="B27" s="21">
         <v>4</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C27" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67" t="s">
+      <c r="D27" s="73"/>
+      <c r="E27" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="68"/>
-    </row>
-    <row r="27" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
-      <c r="B27" s="26">
+      <c r="F27" s="74"/>
+    </row>
+    <row r="28" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="26">
         <v>5</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C28" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="67"/>
-      <c r="E27" s="152" t="s">
+      <c r="D28" s="73"/>
+      <c r="E28" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="153"/>
-    </row>
-    <row r="28" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="29"/>
-      <c r="B28" s="23">
+      <c r="F28" s="171"/>
+    </row>
+    <row r="29" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="29"/>
+      <c r="B29" s="23">
         <v>6</v>
       </c>
-      <c r="C28" s="154" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155" t="s">
+      <c r="C29" s="172"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="156"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="49" t="s">
+      <c r="F29" s="174"/>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B30" s="19">
         <v>1</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C30" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="94"/>
-    </row>
-    <row r="30" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="26">
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69"/>
+    </row>
+    <row r="31" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="32"/>
+      <c r="B31" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="145"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="132"/>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="50"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="148"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="52"/>
-      <c r="B32" s="25" t="s">
+      <c r="C31" s="163"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="85"/>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="50"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="166"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="52"/>
+      <c r="B33" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="149" t="s">
+      <c r="C33" s="167" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="151"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="53"/>
-      <c r="B33" s="23" t="s">
+      <c r="D33" s="168"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="169"/>
+    </row>
+    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="53"/>
+      <c r="B34" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="86" t="s">
+      <c r="C34" s="97" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="87"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="88"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="99"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C17:F17"/>
@@ -3011,23 +3043,6 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3155,11 +3170,11 @@
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -3182,22 +3197,22 @@
       <c r="B10" s="19">
         <v>2</v>
       </c>
-      <c r="C10" s="199" t="s">
+      <c r="C10" s="175" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="200"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="201"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="177"/>
     </row>
     <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20"/>
       <c r="B11" s="21">
         <v>3</v>
       </c>
-      <c r="C11" s="139"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="141"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="162"/>
       <c r="O11" s="54"/>
     </row>
     <row r="12" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3205,10 +3220,10 @@
       <c r="B12" s="23">
         <v>4</v>
       </c>
-      <c r="C12" s="202"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="204"/>
+      <c r="C12" s="178"/>
+      <c r="D12" s="179"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="180"/>
     </row>
     <row r="13" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
@@ -3217,42 +3232,42 @@
       <c r="B13" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="122"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20"/>
       <c r="B14" s="21">
         <v>4</v>
       </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="111"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="123"/>
     </row>
     <row r="15" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20"/>
       <c r="B15" s="21">
         <v>5</v>
       </c>
-      <c r="C15" s="205"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="207"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="183"/>
     </row>
     <row r="16" spans="1:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="27"/>
       <c r="B16" s="23">
         <v>6</v>
       </c>
-      <c r="C16" s="196"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="198"/>
+      <c r="C16" s="198"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="199"/>
+      <c r="F16" s="200"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
@@ -3261,36 +3276,36 @@
       <c r="B17" s="25">
         <v>2</v>
       </c>
-      <c r="C17" s="136" t="s">
+      <c r="C17" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="138"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="159"/>
     </row>
     <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20"/>
       <c r="B18" s="21">
         <v>3</v>
       </c>
-      <c r="C18" s="190" t="s">
+      <c r="C18" s="192" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="191"/>
-      <c r="E18" s="191"/>
-      <c r="F18" s="192"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="194"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="20"/>
       <c r="B19" s="21">
         <v>4</v>
       </c>
-      <c r="C19" s="193" t="s">
+      <c r="C19" s="195" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="194"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="195"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="197"/>
     </row>
     <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24" t="s">
@@ -3299,46 +3314,46 @@
       <c r="B20" s="25">
         <v>1</v>
       </c>
-      <c r="C20" s="185"/>
-      <c r="D20" s="186"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="187"/>
+      <c r="C20" s="187"/>
+      <c r="D20" s="188"/>
+      <c r="E20" s="188"/>
+      <c r="F20" s="189"/>
     </row>
     <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20"/>
       <c r="B21" s="21">
         <v>2</v>
       </c>
-      <c r="C21" s="109" t="s">
+      <c r="C21" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
     </row>
     <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20"/>
       <c r="B22" s="21">
         <v>3</v>
       </c>
-      <c r="C22" s="109" t="s">
+      <c r="C22" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="111"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="123"/>
     </row>
     <row r="23" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="27"/>
       <c r="B23" s="23">
         <v>4</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="188"/>
-      <c r="E23" s="188"/>
-      <c r="F23" s="189"/>
+      <c r="D23" s="190"/>
+      <c r="E23" s="190"/>
+      <c r="F23" s="191"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="24" t="s">
@@ -3347,36 +3362,36 @@
       <c r="B24" s="25">
         <v>3</v>
       </c>
-      <c r="C24" s="133" t="s">
+      <c r="C24" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="134"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="135"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="88"/>
     </row>
     <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="28"/>
       <c r="B25" s="21">
         <v>4</v>
       </c>
-      <c r="C25" s="133" t="s">
+      <c r="C25" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="135"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="88"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="23">
         <v>5</v>
       </c>
-      <c r="C26" s="182" t="s">
+      <c r="C26" s="184" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="183"/>
-      <c r="E26" s="183"/>
-      <c r="F26" s="184"/>
+      <c r="D26" s="185"/>
+      <c r="E26" s="185"/>
+      <c r="F26" s="186"/>
     </row>
     <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
@@ -3385,66 +3400,66 @@
       <c r="B27" s="25">
         <v>2</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="157" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="138"/>
+      <c r="D27" s="158"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="159"/>
     </row>
     <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="28"/>
       <c r="B28" s="56">
         <v>3</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="33"/>
       <c r="B29" s="23">
         <v>4</v>
       </c>
-      <c r="C29" s="104"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="75"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="117"/>
     </row>
     <row r="30" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="59"/>
       <c r="B30" s="60"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="177"/>
-      <c r="F30" s="178"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
     </row>
     <row r="31" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="57"/>
       <c r="B31" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="180"/>
-      <c r="E31" s="180"/>
-      <c r="F31" s="181"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="207"/>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="61" t="s">
         <v>56</v>
       </c>
       <c r="B32" s="62"/>
-      <c r="C32" s="175" t="s">
+      <c r="C32" s="201" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="175"/>
-      <c r="E32" s="175"/>
-      <c r="F32" s="175"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="201"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
@@ -3464,14 +3479,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C20:F20"/>
@@ -3482,12 +3495,14 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3614,11 +3629,11 @@
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="115" t="s">
+      <c r="C8" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -3641,46 +3656,46 @@
       <c r="B10" s="19">
         <v>3</v>
       </c>
-      <c r="C10" s="210" t="s">
+      <c r="C10" s="214" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="211"/>
-      <c r="E10" s="211"/>
-      <c r="F10" s="226"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="216"/>
     </row>
     <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20"/>
       <c r="B11" s="21">
         <v>4</v>
       </c>
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="220" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="213"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="214"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="226"/>
     </row>
     <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20"/>
       <c r="B12" s="21">
         <v>5</v>
       </c>
-      <c r="C12" s="212" t="s">
+      <c r="C12" s="220" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="213"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="214"/>
+      <c r="D12" s="221"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="226"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="22"/>
       <c r="B13" s="23">
         <v>6</v>
       </c>
-      <c r="C13" s="215"/>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="217"/>
+      <c r="C13" s="227"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="229"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
@@ -3689,42 +3704,42 @@
       <c r="B14" s="25">
         <v>3</v>
       </c>
-      <c r="C14" s="208"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-      <c r="F14" s="227"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="225"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20"/>
       <c r="B15" s="21">
         <v>4</v>
       </c>
-      <c r="C15" s="210" t="s">
+      <c r="C15" s="214" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
-      <c r="F15" s="226"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="216"/>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20"/>
       <c r="B16" s="21">
         <v>5</v>
       </c>
-      <c r="C16" s="210"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
-      <c r="F16" s="226"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="215"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="216"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="27"/>
       <c r="B17" s="23">
         <v>6</v>
       </c>
-      <c r="C17" s="218"/>
-      <c r="D17" s="219"/>
-      <c r="E17" s="219"/>
-      <c r="F17" s="228"/>
+      <c r="C17" s="217"/>
+      <c r="D17" s="218"/>
+      <c r="E17" s="218"/>
+      <c r="F17" s="219"/>
     </row>
     <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
@@ -3733,46 +3748,46 @@
       <c r="B18" s="25">
         <v>2</v>
       </c>
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="223" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="209"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="227"/>
+      <c r="D18" s="224"/>
+      <c r="E18" s="224"/>
+      <c r="F18" s="225"/>
     </row>
     <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20"/>
       <c r="B19" s="21">
         <v>3</v>
       </c>
-      <c r="C19" s="212" t="s">
+      <c r="C19" s="220" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="213"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="214"/>
+      <c r="D19" s="221"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="222"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20"/>
       <c r="B20" s="21">
         <v>4</v>
       </c>
-      <c r="C20" s="109" t="s">
+      <c r="C20" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="111"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="123"/>
     </row>
     <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
       <c r="B21" s="23">
         <v>5</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="161"/>
-      <c r="E21" s="161"/>
-      <c r="F21" s="162"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="24" t="s">
@@ -3781,44 +3796,44 @@
       <c r="B22" s="25">
         <v>2</v>
       </c>
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="221"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="222"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="209"/>
+      <c r="F22" s="210"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20"/>
       <c r="B23" s="21">
         <v>3</v>
       </c>
-      <c r="C23" s="212" t="s">
+      <c r="C23" s="220" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="214"/>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="222"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="20"/>
       <c r="B24" s="21">
         <v>4</v>
       </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="141"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="162"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="27"/>
       <c r="B25" s="23">
         <v>5</v>
       </c>
-      <c r="C25" s="157"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="159"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="138"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="24" t="s">
@@ -3827,42 +3842,42 @@
       <c r="B26" s="25">
         <v>3</v>
       </c>
-      <c r="C26" s="136" t="s">
+      <c r="C26" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="137"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="138"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="159"/>
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28"/>
       <c r="B27" s="21">
         <v>4</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="28"/>
       <c r="B28" s="21">
         <v>5</v>
       </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="29"/>
       <c r="B29" s="23">
         <v>6</v>
       </c>
-      <c r="C29" s="223"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="224"/>
-      <c r="F29" s="225"/>
+      <c r="C29" s="211"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="213"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="49" t="s">
@@ -3871,44 +3886,44 @@
       <c r="B30" s="19">
         <v>2</v>
       </c>
-      <c r="C30" s="220"/>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="222"/>
+      <c r="C30" s="208"/>
+      <c r="D30" s="209"/>
+      <c r="E30" s="209"/>
+      <c r="F30" s="210"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="31"/>
       <c r="B31" s="21">
         <v>3</v>
       </c>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="31"/>
       <c r="B32" s="21">
         <v>4</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="74"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="53"/>
       <c r="B33" s="55">
         <v>5</v>
       </c>
-      <c r="C33" s="157"/>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="159"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="138"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
@@ -3928,15 +3943,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
@@ -3947,12 +3959,15 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">

--- a/input/timetable/Биология_.xlsx
+++ b/input/timetable/Биология_.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="141">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -119,12 +122,18 @@
     <t>весенний</t>
   </si>
   <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
+    <t>Белощенко Д.В.</t>
+  </si>
+  <si>
     <t>Систематика низших растений и грибов, п/г 1, А620</t>
   </si>
   <si>
@@ -155,10 +164,25 @@
     <t>Иностранный язык, п/г 1, А502</t>
   </si>
   <si>
+    <t>Ямпольская Т.Д.</t>
+  </si>
+  <si>
+    <t>Стариков В.П.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
     <t>303-31</t>
+  </si>
+  <si>
+    <t>Макарова Т.А.; Сарапульцева Е.С.</t>
+  </si>
+  <si>
+    <t>Сарапульцева Е.С.; Макарова Т.А.</t>
+  </si>
+  <si>
+    <t>Стариков В.П./Самойленко З.А</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -168,18 +192,30 @@
     <t>303-41</t>
   </si>
   <si>
+    <t>Борисенко О.В.</t>
+  </si>
+  <si>
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
     <t>Основы российской государственности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Сердюков Д.В.</t>
+  </si>
+  <si>
     <t>Основы химии, п/г 1, А122</t>
   </si>
   <si>
     <t>Основы химии, п/г 2, А122</t>
   </si>
   <si>
+    <t>Макаров П.Н.</t>
+  </si>
+  <si>
+    <t>Макарова Т.А.</t>
+  </si>
+  <si>
     <t>Гистология с основами цитологии, п/г 1, А620//</t>
   </si>
   <si>
@@ -201,6 +237,9 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Сало В.Э.</t>
+  </si>
+  <si>
     <t>Биохимия и молекулярная биология, п/г1, А131//</t>
   </si>
   <si>
@@ -243,6 +282,12 @@
     <t>Биология                                          (ТО: 02.02.2026-06.04.2026)</t>
   </si>
   <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Самойленко З.А.</t>
+  </si>
+  <si>
     <t>Физиология и биохимия растений (лаб), А639</t>
   </si>
   <si>
@@ -252,6 +297,12 @@
     <t>Спецпрактикум по биоразнообразию и экологии животных (пр),  А622,623</t>
   </si>
   <si>
+    <t>Берников К.А., Сарапульцева Е.С.</t>
+  </si>
+  <si>
+    <t>Берников К.А., Сарапульцева Е.С</t>
+  </si>
+  <si>
     <t>Спецпрактикум по биоразнообразию и экологии растений (пр), А639</t>
   </si>
   <si>
@@ -267,6 +318,15 @@
     <t>Производственная практика, по профилю профессиональной деятельности, А639</t>
   </si>
   <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
+    <t>Грамма Д.В.</t>
+  </si>
+  <si>
+    <t>Чудова Е.С.</t>
+  </si>
+  <si>
     <t>История России (пр). Г224//</t>
   </si>
   <si>
@@ -276,18 +336,27 @@
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
     <t>Зоология позвоночных (лек), А615//  Систематика споровых и семенных растений (лек), А615</t>
   </si>
   <si>
     <t>Правоведение (лек 32ч)</t>
   </si>
   <si>
+    <t>Власюк Е.И.</t>
+  </si>
+  <si>
     <t>Правоведение (пр), А603</t>
   </si>
   <si>
     <t>Иностранный язык, п/г 1, А501</t>
   </si>
   <si>
+    <t>Собиров Б.Ш.</t>
+  </si>
+  <si>
     <t>Иммунология (лек)/(лаб), А628</t>
   </si>
   <si>
@@ -324,9 +393,30 @@
     <t>Зоология беспозвоночных (лек), А613// Систематика низших растений и грибов (лек), А613</t>
   </si>
   <si>
+    <t>Сарапульцева Е.С./Макаров П.Н.</t>
+  </si>
+  <si>
+    <t>Федоряева В.Н.</t>
+  </si>
+  <si>
+    <t>Ямпольская Т.Д.;Самойленко З.А</t>
+  </si>
+  <si>
+    <t>Берников К.А. ; Шукурова И.В.</t>
+  </si>
+  <si>
+    <t>Шукурова И.В.;Берников К.А.</t>
+  </si>
+  <si>
+    <t>Самойленко З.А; Ямпольская Т.Д.</t>
+  </si>
+  <si>
     <t>Основы российской государственности (пр), А636</t>
   </si>
   <si>
+    <t>Умарова М.М.</t>
+  </si>
+  <si>
     <t>//История России (пр). Г224</t>
   </si>
   <si>
@@ -336,16 +426,28 @@
     <t xml:space="preserve"> Основы химии (лек), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Лоншакова -Мукина В.И.</t>
+  </si>
+  <si>
     <t>//  Основы предпринимательской деятельности (пр), У902</t>
   </si>
   <si>
     <t>//Биохимия и молекулярная биология (лек),ЭОиДОТ</t>
   </si>
   <si>
+    <t>Лоншакова-Мукина В.И.</t>
+  </si>
+  <si>
+    <t>Скоробогатова А.В.</t>
+  </si>
+  <si>
     <t>Методика преподавания биологии в школе (лек), А615</t>
   </si>
   <si>
     <t>Методика преподавания биологии в школе (пр), А615</t>
+  </si>
+  <si>
+    <t>Фаррахова Г.Р.</t>
   </si>
 </sst>
 </file>
@@ -457,7 +559,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,6 +578,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -487,7 +595,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -595,6 +703,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -671,6 +837,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1079,6 +1258,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1102,6 +1296,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1134,7 +1339,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1171,16 +1376,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1189,19 +1397,21 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1215,10 +1425,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1227,10 +1437,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
@@ -1241,26 +1451,27 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1269,222 +1480,291 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1499,211 +1779,173 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2026,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2035,12 +2277,13 @@
     <col min="4" max="4" width="17.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="9.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2048,15 +2291,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2064,436 +2307,506 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
+      <c r="C6" s="43" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="43">
+      <c r="E6" s="46">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
-      <c r="E7" s="42" t="s">
-        <v>66</v>
+      <c r="E7" s="45" t="s">
+        <v>79</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="80"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21">
+      <c r="C10" s="159"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="161"/>
+      <c r="G10" s="78"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22">
         <v>2</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="66"/>
-    </row>
-    <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21">
+      <c r="C11" s="149" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="22">
         <v>3</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="166" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="77" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
+        <v>5</v>
+      </c>
+      <c r="C13" s="156" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="93" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="28">
+        <v>1</v>
+      </c>
+      <c r="C14" s="153"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="78"/>
+    </row>
+    <row r="15" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22">
+        <v>2</v>
+      </c>
+      <c r="C15" s="149" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="118"/>
+      <c r="G15" s="77" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22">
+        <v>3</v>
+      </c>
+      <c r="C16" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="101"/>
+      <c r="G16" s="77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="30"/>
+      <c r="B17" s="25">
+        <v>4</v>
+      </c>
+      <c r="C17" s="162" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="163"/>
+      <c r="E17" s="164"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="88"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23">
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="28">
+        <v>1</v>
+      </c>
+      <c r="C18" s="150"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="88"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22">
+        <v>2</v>
+      </c>
+      <c r="C19" s="149" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="77" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22">
+        <v>3</v>
+      </c>
+      <c r="C20" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="30"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="70"/>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="28">
+        <v>1</v>
+      </c>
+      <c r="C22" s="96"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="98"/>
+      <c r="G22" s="77" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22">
+        <v>2</v>
+      </c>
+      <c r="C23" s="115"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="118"/>
+      <c r="G23" s="77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="21"/>
+      <c r="B24" s="22">
+        <v>3</v>
+      </c>
+      <c r="C24" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="143"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="77" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="30"/>
+      <c r="B25" s="25">
+        <v>4</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="92" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="28">
+        <v>1</v>
+      </c>
+      <c r="C26" s="145" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="146"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31"/>
+      <c r="B27" s="22">
+        <v>2</v>
+      </c>
+      <c r="C27" s="112" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="84" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="68"/>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="32"/>
+      <c r="B29" s="25">
         <v>5</v>
       </c>
-      <c r="C13" s="75" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="77"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="C29" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="28">
         <v>1</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
-    </row>
-    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21">
+      <c r="C30" s="125" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="126"/>
+      <c r="E30" s="126"/>
+      <c r="F30" s="127"/>
+      <c r="G30" s="72"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="34"/>
+      <c r="B31" s="22">
         <v>2</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C31" s="122"/>
+      <c r="D31" s="123"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="68"/>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="35"/>
+      <c r="B32" s="29">
+        <v>3</v>
+      </c>
+      <c r="C32" s="134"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="136"/>
+      <c r="G32" s="69"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="36"/>
+      <c r="B33" s="25">
+        <v>4</v>
+      </c>
+      <c r="C33" s="137"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="70"/>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="131"/>
+      <c r="D34" s="132"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="133"/>
+      <c r="G34" s="71"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="66"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21">
-        <v>3</v>
-      </c>
-      <c r="C16" s="81" t="s">
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="82" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="41"/>
+      <c r="B36" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="128" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="129"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="76" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="41"/>
+      <c r="B37" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="128" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="129"/>
+      <c r="E37" s="129"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="74"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="27"/>
-      <c r="B17" s="23">
-        <v>4</v>
-      </c>
-      <c r="C17" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="85"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25">
-        <v>1</v>
-      </c>
-      <c r="C18" s="67"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21">
-        <v>2</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="66"/>
-    </row>
-    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21">
-        <v>3</v>
-      </c>
-      <c r="C20" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="27"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="132"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="127"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="129"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21">
-        <v>2</v>
-      </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="66"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="20"/>
-      <c r="B24" s="21">
-        <v>3</v>
-      </c>
-      <c r="C24" s="121" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="27"/>
-      <c r="B25" s="23">
-        <v>4</v>
-      </c>
-      <c r="C25" s="133" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="117"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="25">
-        <v>1</v>
-      </c>
-      <c r="C26" s="124" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="126"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28"/>
-      <c r="B27" s="21">
-        <v>2</v>
-      </c>
-      <c r="C27" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="94"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="28"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="91"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="29"/>
-      <c r="B29" s="23">
-        <v>5</v>
-      </c>
-      <c r="C29" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="25">
-        <v>1</v>
-      </c>
-      <c r="C30" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="21">
-        <v>2</v>
-      </c>
-      <c r="C31" s="100"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="102"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32"/>
-      <c r="B32" s="26">
-        <v>3</v>
-      </c>
-      <c r="C32" s="112"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="33"/>
-      <c r="B33" s="23">
-        <v>4</v>
-      </c>
-      <c r="C33" s="115"/>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="117"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="111"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="108"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="106" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="32"/>
+      <c r="B38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="119" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="120"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="108"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="29"/>
-      <c r="B38" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="99"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>15</v>
       </c>
@@ -2503,12 +2816,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C23:D23"/>
@@ -2525,20 +2846,12 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2569,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2578,10 +2891,11 @@
     <col min="4" max="4" width="20" style="2" customWidth="1"/>
     <col min="5" max="5" width="21" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2589,15 +2903,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2605,402 +2919,460 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="46">
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42" t="s">
-        <v>46</v>
+      <c r="D7" s="44"/>
+      <c r="E7" s="45" t="s">
+        <v>54</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="103" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21">
+      <c r="C10" s="125" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="78" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22">
         <v>2</v>
       </c>
-      <c r="C11" s="81" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73" t="s">
+      <c r="C11" s="99" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="101"/>
+      <c r="G11" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="29">
+        <v>3</v>
+      </c>
+      <c r="C12" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="94"/>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="21"/>
+      <c r="B13" s="25">
+        <v>6</v>
+      </c>
+      <c r="C13" s="175" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="177"/>
+      <c r="G13" s="94" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="28">
+        <v>3</v>
+      </c>
+      <c r="C14" s="153" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="74"/>
-    </row>
-    <row r="12" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20"/>
-      <c r="B12" s="26">
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22">
+        <v>4</v>
+      </c>
+      <c r="C15" s="199" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="203"/>
+      <c r="G15" s="77" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22">
+        <v>5</v>
+      </c>
+      <c r="C16" s="201" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="204"/>
+      <c r="G16" s="77" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="30"/>
+      <c r="B17" s="25">
+        <v>6</v>
+      </c>
+      <c r="C17" s="193"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="70"/>
+    </row>
+    <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="28">
+        <v>1</v>
+      </c>
+      <c r="C18" s="196"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="197"/>
+      <c r="F18" s="198"/>
+      <c r="G18" s="72"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22">
+        <v>2</v>
+      </c>
+      <c r="C19" s="142" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="77" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22">
         <v>3</v>
       </c>
-      <c r="C12" s="121" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="123"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="20"/>
-      <c r="B13" s="23">
+      <c r="C20" s="205"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="207"/>
+      <c r="G20" s="77"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="30"/>
+      <c r="B21" s="25">
+        <v>4</v>
+      </c>
+      <c r="C21" s="190"/>
+      <c r="D21" s="191"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="192"/>
+      <c r="G21" s="70"/>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="28">
+        <v>1</v>
+      </c>
+      <c r="C22" s="169" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="170"/>
+      <c r="E22" s="170"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="78" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22">
+        <v>2</v>
+      </c>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="75"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="30"/>
+      <c r="B24" s="25">
+        <v>3</v>
+      </c>
+      <c r="C24" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="177"/>
+      <c r="G24" s="70"/>
+    </row>
+    <row r="25" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="28">
+        <v>2</v>
+      </c>
+      <c r="C25" s="125" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="78" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="31"/>
+      <c r="B26" s="20">
+        <v>3</v>
+      </c>
+      <c r="C26" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="87" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31"/>
+      <c r="B27" s="22">
+        <v>4</v>
+      </c>
+      <c r="C27" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="101"/>
+      <c r="G27" s="77" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="51"/>
+      <c r="B28" s="29">
+        <v>5</v>
+      </c>
+      <c r="C28" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="100"/>
+      <c r="E28" s="185" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="186"/>
+      <c r="G28" s="77" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="32"/>
+      <c r="B29" s="25">
         <v>6</v>
       </c>
-      <c r="C13" s="145" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" s="146"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="147"/>
-    </row>
-    <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="25">
-        <v>3</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
-    </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21">
-        <v>4</v>
-      </c>
-      <c r="C15" s="148" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="149"/>
-      <c r="E15" s="149" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="152"/>
-    </row>
-    <row r="16" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21">
-        <v>5</v>
-      </c>
-      <c r="C16" s="150" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="153"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="27"/>
-      <c r="B17" s="23">
-        <v>6</v>
-      </c>
-      <c r="C17" s="139"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="141"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="C29" s="187"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="189"/>
+      <c r="G29" s="79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20">
         <v>1</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="144"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21">
+      <c r="C30" s="150" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="151"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="87"/>
+    </row>
+    <row r="31" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="35"/>
+      <c r="B31" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="121" t="s">
+      <c r="C31" s="178"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="86"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="179"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="55"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="56"/>
+      <c r="B33" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="182" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="184"/>
+      <c r="G33" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-    </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21">
-        <v>3</v>
-      </c>
-      <c r="C20" s="154"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
-      <c r="F20" s="156"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="27"/>
-      <c r="B21" s="23">
-        <v>4</v>
-      </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="138"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1</v>
-      </c>
-      <c r="C22" s="157" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="159"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21">
-        <v>2</v>
-      </c>
-      <c r="C23" s="160"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="162"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="27"/>
-      <c r="B24" s="23">
-        <v>3</v>
-      </c>
-      <c r="C24" s="145" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="147"/>
-    </row>
-    <row r="25" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="25">
-        <v>2</v>
-      </c>
-      <c r="C25" s="103" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28"/>
-      <c r="B26" s="19">
-        <v>3</v>
-      </c>
-      <c r="C26" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74"/>
-    </row>
-    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28"/>
-      <c r="B27" s="21">
-        <v>4</v>
-      </c>
-      <c r="C27" s="81" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="74"/>
-    </row>
-    <row r="28" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
-      <c r="B28" s="26">
-        <v>5</v>
-      </c>
-      <c r="C28" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="170" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="171"/>
-    </row>
-    <row r="29" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="29"/>
-      <c r="B29" s="23">
-        <v>6</v>
-      </c>
-      <c r="C29" s="172"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="174"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="19">
-        <v>1</v>
-      </c>
-      <c r="C30" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-    </row>
-    <row r="31" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="32"/>
-      <c r="B31" s="26">
-        <v>2</v>
-      </c>
-      <c r="C31" s="163"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="85"/>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="50"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="164"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="166"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="52"/>
-      <c r="B33" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="167" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="168"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="169"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53"/>
-      <c r="B34" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="99"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="57"/>
+      <c r="B34" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -3010,23 +3382,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C8:E8"/>
@@ -3043,6 +3398,23 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3073,7 +3445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3082,10 +3454,11 @@
     <col min="4" max="4" width="21.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3093,15 +3466,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3109,364 +3482,415 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="46">
         <v>3</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42" t="s">
-        <v>44</v>
+      <c r="D7" s="44"/>
+      <c r="E7" s="45" t="s">
+        <v>49</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+    </row>
+    <row r="9" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="20">
         <v>2</v>
       </c>
-      <c r="C10" s="175" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="177"/>
-    </row>
-    <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21">
+      <c r="C10" s="232" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="82" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22">
         <v>3</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="161"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="162"/>
-      <c r="O11" s="54"/>
-    </row>
-    <row r="12" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="83"/>
+      <c r="P11" s="58"/>
+    </row>
+    <row r="12" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>4</v>
       </c>
-      <c r="C12" s="178"/>
-      <c r="D12" s="179"/>
-      <c r="E12" s="179"/>
-      <c r="F12" s="180"/>
-    </row>
-    <row r="13" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
-    </row>
-    <row r="14" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
+      <c r="C12" s="235"/>
+      <c r="D12" s="236"/>
+      <c r="E12" s="236"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="68"/>
+    </row>
+    <row r="13" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="153" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="154"/>
+      <c r="E13" s="154"/>
+      <c r="F13" s="155"/>
+      <c r="G13" s="78"/>
+    </row>
+    <row r="14" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22">
         <v>4</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="123"/>
-    </row>
-    <row r="15" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21">
+      <c r="C14" s="142"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="83"/>
+    </row>
+    <row r="15" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22">
         <v>5</v>
       </c>
-      <c r="C15" s="181"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="183"/>
-    </row>
-    <row r="16" spans="1:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="27"/>
-      <c r="B16" s="23">
+      <c r="C15" s="238"/>
+      <c r="D15" s="239"/>
+      <c r="E15" s="239"/>
+      <c r="F15" s="240"/>
+      <c r="G15" s="83"/>
+    </row>
+    <row r="16" spans="1:16" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="30"/>
+      <c r="B16" s="25">
         <v>6</v>
       </c>
-      <c r="C16" s="198"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
-      <c r="F16" s="200"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="25">
+      <c r="C16" s="229"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="231"/>
+      <c r="G16" s="70"/>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="28">
         <v>2</v>
       </c>
-      <c r="C17" s="157" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="159"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21">
+      <c r="C17" s="169" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="170"/>
+      <c r="E17" s="170"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22">
         <v>3</v>
       </c>
-      <c r="C18" s="192" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="193"/>
-      <c r="E18" s="193"/>
-      <c r="F18" s="194"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21">
+      <c r="C18" s="223" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="224"/>
+      <c r="E18" s="224"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22">
         <v>4</v>
       </c>
-      <c r="C19" s="195" t="s">
+      <c r="C19" s="226" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="227"/>
+      <c r="E19" s="227"/>
+      <c r="F19" s="228"/>
+      <c r="G19" s="91" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="28">
+        <v>1</v>
+      </c>
+      <c r="C20" s="218"/>
+      <c r="D20" s="219"/>
+      <c r="E20" s="219"/>
+      <c r="F20" s="220"/>
+      <c r="G20" s="72"/>
+    </row>
+    <row r="21" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22">
+        <v>2</v>
+      </c>
+      <c r="C21" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22">
+        <v>3</v>
+      </c>
+      <c r="C22" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="25">
+        <v>4</v>
+      </c>
+      <c r="C23" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="79" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="166" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="31"/>
+      <c r="B25" s="22">
+        <v>4</v>
+      </c>
+      <c r="C25" s="166" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="196"/>
-      <c r="E19" s="196"/>
-      <c r="F19" s="197"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="25">
-        <v>1</v>
-      </c>
-      <c r="C20" s="187"/>
-      <c r="D20" s="188"/>
-      <c r="E20" s="188"/>
-      <c r="F20" s="189"/>
-    </row>
-    <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21">
+      <c r="D25" s="167"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="25">
+        <v>5</v>
+      </c>
+      <c r="C26" s="215" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="217"/>
+      <c r="G26" s="86" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="28">
         <v>2</v>
       </c>
-      <c r="C21" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-    </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21">
+      <c r="C27" s="169" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="170"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="78" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="60">
         <v>3</v>
       </c>
-      <c r="C22" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
-      <c r="F22" s="123"/>
-    </row>
-    <row r="23" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="27"/>
-      <c r="B23" s="23">
+      <c r="C28" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="77" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="36"/>
+      <c r="B29" s="25">
         <v>4</v>
       </c>
-      <c r="C23" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="190"/>
-      <c r="E23" s="190"/>
-      <c r="F23" s="191"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="25">
-        <v>3</v>
-      </c>
-      <c r="C24" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="28"/>
-      <c r="B25" s="21">
-        <v>4</v>
-      </c>
-      <c r="C25" s="86" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="88"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="23">
-        <v>5</v>
-      </c>
-      <c r="C26" s="184" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="186"/>
-    </row>
-    <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="25">
-        <v>2</v>
-      </c>
-      <c r="C27" s="157" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="159"/>
-    </row>
-    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="28"/>
-      <c r="B28" s="56">
-        <v>3</v>
-      </c>
-      <c r="C28" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-    </row>
-    <row r="29" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="33"/>
-      <c r="B29" s="23">
-        <v>4</v>
-      </c>
-      <c r="C29" s="115"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="117"/>
-    </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="59"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="202"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="204"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="57"/>
-      <c r="B31" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="205" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="206"/>
-      <c r="E31" s="206"/>
-      <c r="F31" s="207"/>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="201" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="201"/>
-      <c r="E32" s="201"/>
-      <c r="F32" s="201"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="70"/>
+    </row>
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="63"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="210"/>
+      <c r="E30" s="210"/>
+      <c r="F30" s="211"/>
+      <c r="G30" s="65"/>
+    </row>
+    <row r="31" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="61"/>
+      <c r="B31" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="212" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="214"/>
+      <c r="G31" s="89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="67"/>
+      <c r="C32" s="208" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="208"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -3479,12 +3903,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C20:F20"/>
@@ -3495,14 +3921,12 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3533,7 +3957,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3541,10 +3965,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
     <col min="5" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3552,15 +3977,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3568,372 +3993,421 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="43">
+      <c r="C6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="46">
         <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42" t="s">
-        <v>67</v>
+      <c r="D7" s="44"/>
+      <c r="E7" s="45" t="s">
+        <v>80</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="20">
         <v>3</v>
       </c>
-      <c r="C10" s="214" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="215"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="216"/>
-    </row>
-    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21">
+      <c r="C10" s="244" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="80" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22">
         <v>4</v>
       </c>
-      <c r="C11" s="220" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="221"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="226"/>
-    </row>
-    <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21">
+      <c r="C11" s="247" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="22">
         <v>5</v>
       </c>
-      <c r="C12" s="220" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="221"/>
-      <c r="E12" s="221"/>
-      <c r="F12" s="226"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23">
+      <c r="C12" s="247" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>6</v>
       </c>
-      <c r="C13" s="227"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="228"/>
-      <c r="F13" s="229"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="C13" s="250"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="86"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="28">
         <v>3</v>
       </c>
-      <c r="C14" s="223"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="224"/>
-      <c r="F14" s="225"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21">
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="242"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="82"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22">
         <v>4</v>
       </c>
-      <c r="C15" s="214" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="215"/>
-      <c r="E15" s="215"/>
-      <c r="F15" s="216"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21">
+      <c r="C15" s="244" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="80" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22">
         <v>5</v>
       </c>
-      <c r="C16" s="214"/>
-      <c r="D16" s="215"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="216"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="27"/>
-      <c r="B17" s="23">
+      <c r="C16" s="244"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="80"/>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="30"/>
+      <c r="B17" s="25">
         <v>6</v>
       </c>
-      <c r="C17" s="217"/>
-      <c r="D17" s="218"/>
-      <c r="E17" s="218"/>
-      <c r="F17" s="219"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="C17" s="253"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="28">
         <v>2</v>
       </c>
-      <c r="C18" s="223" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="224"/>
-      <c r="E18" s="224"/>
-      <c r="F18" s="225"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21">
+      <c r="C18" s="241" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="82" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22">
         <v>3</v>
       </c>
-      <c r="C19" s="220" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="221"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="222"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21">
+      <c r="C19" s="247" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22">
         <v>4</v>
       </c>
-      <c r="C20" s="121" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="27"/>
-      <c r="B21" s="23">
+      <c r="C20" s="142" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="83" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="30"/>
+      <c r="B21" s="25">
         <v>5</v>
       </c>
-      <c r="C21" s="139"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="141"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="25">
+      <c r="C21" s="193"/>
+      <c r="D21" s="194"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="195"/>
+      <c r="G21" s="73"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="28">
         <v>2</v>
       </c>
-      <c r="C22" s="208" t="s">
+      <c r="C22" s="257" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="259"/>
+      <c r="G22" s="82" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22">
+        <v>3</v>
+      </c>
+      <c r="C23" s="247" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="209"/>
-      <c r="E22" s="209"/>
-      <c r="F22" s="210"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21">
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="256"/>
+      <c r="G23" s="80" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="21"/>
+      <c r="B24" s="22">
+        <v>4</v>
+      </c>
+      <c r="C24" s="172"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="30"/>
+      <c r="B25" s="25">
+        <v>5</v>
+      </c>
+      <c r="C25" s="190"/>
+      <c r="D25" s="191"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="192"/>
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="28">
         <v>3</v>
       </c>
-      <c r="C23" s="220" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="221"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="222"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="20"/>
-      <c r="B24" s="21">
+      <c r="C26" s="169" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="170"/>
+      <c r="E26" s="170"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="85"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31"/>
+      <c r="B27" s="22">
         <v>4</v>
       </c>
-      <c r="C24" s="160"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="162"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="27"/>
-      <c r="B25" s="23">
+      <c r="C27" s="99"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="83"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="22">
         <v>5</v>
       </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="138"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="25">
+      <c r="C28" s="99"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="83"/>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="32"/>
+      <c r="B29" s="25">
+        <v>6</v>
+      </c>
+      <c r="C29" s="260"/>
+      <c r="D29" s="261"/>
+      <c r="E29" s="261"/>
+      <c r="F29" s="262"/>
+      <c r="G29" s="73"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20">
+        <v>2</v>
+      </c>
+      <c r="C30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="258"/>
+      <c r="F30" s="259"/>
+      <c r="G30" s="74"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="34"/>
+      <c r="B31" s="22">
         <v>3</v>
       </c>
-      <c r="C26" s="157" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="159"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28"/>
-      <c r="B27" s="21">
+      <c r="C31" s="99" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="95" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="34"/>
+      <c r="B32" s="22">
         <v>4</v>
       </c>
-      <c r="C27" s="81"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="28"/>
-      <c r="B28" s="21">
+      <c r="C32" s="99" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="95" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="57"/>
+      <c r="B33" s="59">
         <v>5</v>
       </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="29"/>
-      <c r="B29" s="23">
-        <v>6</v>
-      </c>
-      <c r="C29" s="211"/>
-      <c r="D29" s="212"/>
-      <c r="E29" s="212"/>
-      <c r="F29" s="213"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="19">
-        <v>2</v>
-      </c>
-      <c r="C30" s="208"/>
-      <c r="D30" s="209"/>
-      <c r="E30" s="209"/>
-      <c r="F30" s="210"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="21">
-        <v>3</v>
-      </c>
-      <c r="C31" s="81" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="31"/>
-      <c r="B32" s="21">
-        <v>4</v>
-      </c>
-      <c r="C32" s="81" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="74"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="53"/>
-      <c r="B33" s="55">
-        <v>5</v>
-      </c>
-      <c r="C33" s="136"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="138"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="190"/>
+      <c r="D33" s="191"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="192"/>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3943,12 +4417,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
@@ -3959,15 +4436,12 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
